--- a/AAII_Financials/Yearly/KNRRY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/KNRRY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="92">
   <si>
     <t>KNRRY</t>
   </si>
@@ -295,6 +295,9 @@
   </si>
   <si>
     <t xml:space="preserve">Change In Cash and Cash Equivalents </t>
+  </si>
+  <si>
+    <t>NA</t>
   </si>
 </sst>
 </file>
@@ -302,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -344,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -653,135 +656,147 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L7" s="2"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8278700</v>
+      </c>
+      <c r="E8" s="3">
         <v>8885700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>7753300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7720600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7624300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>7866500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>7629800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>7427100</v>
       </c>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3892000</v>
+      </c>
+      <c r="E9" s="3">
         <v>4590500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>4109800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3899000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3749900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3960700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3873000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3693100</v>
       </c>
-      <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4386700</v>
+      </c>
+      <c r="E10" s="3">
         <v>4295300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3643500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3821600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3874400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3905800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3756800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3734100</v>
       </c>
-      <c r="K10" s="3"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -793,35 +808,39 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E12" s="3">
         <v>482800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>385900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>396100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>391800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>363100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>361300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>392700</v>
       </c>
-      <c r="K12" s="3"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -846,63 +865,72 @@
       <c r="J13" s="3">
         <v>0</v>
       </c>
-      <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K13" s="3">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E14" s="3">
         <v>33600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>19400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-6700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>24400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>72200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>18700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-7300</v>
       </c>
-      <c r="K14" s="3"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>405500</v>
+      </c>
+      <c r="E15" s="3">
         <v>367400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>325600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>320700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>328500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>278900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>213500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>253900</v>
       </c>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -911,62 +939,69 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>7335900</v>
+      </c>
+      <c r="E17" s="3">
         <v>7906100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6972600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6702400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6598900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6692900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6497600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6348900</v>
       </c>
-      <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>942900</v>
+      </c>
+      <c r="E18" s="3">
         <v>979700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>780700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1018200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1025300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1173600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1132100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1078300</v>
       </c>
-      <c r="K18" s="3"/>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3"/>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -978,143 +1013,159 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>225900</v>
+      </c>
+      <c r="E20" s="3">
         <v>15500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>23600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-23000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>24800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>32800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>71800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>44200</v>
       </c>
-      <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3"/>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>1122500</v>
+      </c>
+      <c r="E21" s="3">
         <v>1331600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1082700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1361900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1329100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1419600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1273800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1288000</v>
       </c>
-      <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3"/>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>111400</v>
+      </c>
+      <c r="E22" s="3">
         <v>111700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>54000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>64200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>81700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>81600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>62300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>46600</v>
       </c>
-      <c r="K22" s="3"/>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3"/>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>668200</v>
+      </c>
+      <c r="E23" s="3">
         <v>854200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>736100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1001700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>918100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1018000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1002400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1023600</v>
       </c>
-      <c r="K23" s="3"/>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3"/>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>174000</v>
+      </c>
+      <c r="E24" s="3">
         <v>217300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>195100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>265500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>267100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>308700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>281700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>318500</v>
       </c>
-      <c r="K24" s="3"/>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3"/>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1139,63 +1190,72 @@
       <c r="J25" s="3">
         <v>0</v>
       </c>
-      <c r="K25" s="3"/>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K25" s="3">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3"/>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>494200</v>
+      </c>
+      <c r="E26" s="3">
         <v>636900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>541000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>736200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>651000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>709300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>720700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>705100</v>
       </c>
-      <c r="K26" s="3"/>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3"/>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>461200</v>
+      </c>
+      <c r="E27" s="3">
         <v>610700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>522900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>706600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>606100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>660300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>678700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>643000</v>
       </c>
-      <c r="K27" s="3"/>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3"/>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1220,9 +1280,12 @@
       <c r="J28" s="3">
         <v>0</v>
       </c>
-      <c r="K28" s="3"/>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K28" s="3">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3"/>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1247,9 +1310,12 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3"/>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3"/>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1274,9 +1340,12 @@
       <c r="J30" s="3">
         <v>0</v>
       </c>
-      <c r="K30" s="3"/>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K30" s="3">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3"/>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1301,63 +1370,72 @@
       <c r="J31" s="3">
         <v>0</v>
       </c>
-      <c r="K31" s="3"/>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K31" s="3">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3"/>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>-225900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-15500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-23600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>23000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-24800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-32800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-71800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-44200</v>
       </c>
-      <c r="K32" s="3"/>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3"/>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>461200</v>
+      </c>
+      <c r="E33" s="3">
         <v>610700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>522900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>706600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>606100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>660300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>678700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>643000</v>
       </c>
-      <c r="K33" s="3"/>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3"/>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1382,68 +1460,77 @@
       <c r="J34" s="3">
         <v>0</v>
       </c>
-      <c r="K34" s="3"/>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K34" s="3">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3"/>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>461200</v>
+      </c>
+      <c r="E35" s="3">
         <v>610700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>522900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>706600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>606100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>660300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>678700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>643000</v>
       </c>
-      <c r="K35" s="3"/>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3"/>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2"/>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L38" s="2"/>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1455,8 +1542,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1468,35 +1556,39 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>2342900</v>
+      </c>
+      <c r="E41" s="3">
         <v>1427400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1434800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1569700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2785400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2110600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2010600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1921300</v>
       </c>
-      <c r="K41" s="3"/>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="3"/>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -1521,198 +1613,222 @@
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3"/>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3"/>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>1683500</v>
+      </c>
+      <c r="E43" s="3">
         <v>1817600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1699500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1634400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1625700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1554500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1709800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1669800</v>
       </c>
-      <c r="K43" s="3"/>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3"/>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>1258900</v>
+      </c>
+      <c r="E44" s="3">
         <v>1262700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1220400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1139700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1033100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>914600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>957600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>899200</v>
       </c>
-      <c r="K44" s="3"/>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3"/>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>322900</v>
+      </c>
+      <c r="E45" s="3">
         <v>487200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>350000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>134400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>179400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>159600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>57700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>141500</v>
       </c>
-      <c r="K45" s="3"/>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3"/>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>5608200</v>
+      </c>
+      <c r="E46" s="3">
         <v>4994800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4704800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4478200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5623600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4739300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4774900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4631700</v>
       </c>
-      <c r="K46" s="3"/>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L46" s="3"/>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>37600</v>
+      </c>
+      <c r="E47" s="3">
         <v>67200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>85000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>25100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>30200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>18600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2300</v>
       </c>
-      <c r="K47" s="3"/>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3"/>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>1964100</v>
+      </c>
+      <c r="E48" s="3">
         <v>1798200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1689700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1754600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1615500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1435100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1137500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1203900</v>
       </c>
-      <c r="K48" s="3"/>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3"/>
+    </row>
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>1880900</v>
+      </c>
+      <c r="E49" s="3">
         <v>1620900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1560300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1089900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1039500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>848200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>640000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>642800</v>
       </c>
-      <c r="K49" s="3"/>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3"/>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -1737,9 +1853,12 @@
       <c r="J50" s="3">
         <v>0</v>
       </c>
-      <c r="K50" s="3"/>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K50" s="3">
+        <v>0</v>
+      </c>
+      <c r="L50" s="3"/>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -1764,36 +1883,42 @@
       <c r="J51" s="3">
         <v>0</v>
       </c>
-      <c r="K51" s="3"/>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K51" s="3">
+        <v>0</v>
+      </c>
+      <c r="L51" s="3"/>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>225700</v>
+      </c>
+      <c r="E52" s="3">
         <v>467000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>425800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>634700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>537300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>458600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>425800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>294500</v>
       </c>
-      <c r="K52" s="3"/>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3"/>
+    </row>
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -1818,36 +1943,42 @@
       <c r="J53" s="3">
         <v>0</v>
       </c>
-      <c r="K53" s="3"/>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K53" s="3">
+        <v>0</v>
+      </c>
+      <c r="L53" s="3"/>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>9970600</v>
+      </c>
+      <c r="E54" s="3">
         <v>9117500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8701000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8187400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>9039700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7683500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7169900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6877300</v>
       </c>
-      <c r="K54" s="3"/>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L54" s="3"/>
+    </row>
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -1859,8 +1990,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -1872,170 +2004,189 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>1168200</v>
+      </c>
+      <c r="E57" s="3">
         <v>1328100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1297400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1326100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1257100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1085700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1140300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1073600</v>
       </c>
-      <c r="K57" s="3"/>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3"/>
+    </row>
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>74600</v>
+      </c>
+      <c r="E58" s="3">
         <v>177800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>285400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>180500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1386400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>255800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>81100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>47700</v>
       </c>
-      <c r="K58" s="3"/>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3"/>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>2217900</v>
+      </c>
+      <c r="E59" s="3">
         <v>1228200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1191100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1552000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1524300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1343500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1406500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1553600</v>
       </c>
-      <c r="K59" s="3"/>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3"/>
+    </row>
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>3480400</v>
+      </c>
+      <c r="E60" s="3">
         <v>2852000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2866900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3067600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4271600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2819800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2713500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2766300</v>
       </c>
-      <c r="K60" s="3"/>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L60" s="3"/>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>499700</v>
+      </c>
+      <c r="E61" s="3">
         <v>2098100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2034800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1398800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1356500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1790000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1648500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>869600</v>
       </c>
-      <c r="K61" s="3"/>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3"/>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>2370500</v>
+      </c>
+      <c r="E62" s="3">
         <v>521100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>530000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>427200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>461600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>437100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>489100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>388200</v>
       </c>
-      <c r="K62" s="3"/>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3"/>
+    </row>
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2060,9 +2211,12 @@
       <c r="J63" s="3">
         <v>0</v>
       </c>
-      <c r="K63" s="3"/>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K63" s="3">
+        <v>0</v>
+      </c>
+      <c r="L63" s="3"/>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2087,9 +2241,12 @@
       <c r="J64" s="3">
         <v>0</v>
       </c>
-      <c r="K64" s="3"/>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K64" s="3">
+        <v>0</v>
+      </c>
+      <c r="L64" s="3"/>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -2114,36 +2271,42 @@
       <c r="J65" s="3">
         <v>0</v>
       </c>
-      <c r="K65" s="3"/>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K65" s="3">
+        <v>0</v>
+      </c>
+      <c r="L65" s="3"/>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>6733600</v>
+      </c>
+      <c r="E66" s="3">
         <v>5908100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5892500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5428900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6689100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5549600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5329900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4480900</v>
       </c>
-      <c r="K66" s="3"/>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L66" s="3"/>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -2155,8 +2318,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -2181,9 +2345,12 @@
       <c r="J68" s="3">
         <v>0</v>
       </c>
-      <c r="K68" s="3"/>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K68" s="3">
+        <v>0</v>
+      </c>
+      <c r="L68" s="3"/>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -2208,9 +2375,12 @@
       <c r="J69" s="3">
         <v>0</v>
       </c>
-      <c r="K69" s="3"/>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K69" s="3">
+        <v>0</v>
+      </c>
+      <c r="L69" s="3"/>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -2235,9 +2405,12 @@
       <c r="J70" s="3">
         <v>0</v>
       </c>
-      <c r="K70" s="3"/>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3"/>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -2262,36 +2435,42 @@
       <c r="J71" s="3">
         <v>0</v>
       </c>
-      <c r="K71" s="3"/>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K71" s="3">
+        <v>0</v>
+      </c>
+      <c r="L71" s="3"/>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>3120900</v>
+      </c>
+      <c r="E72" s="3">
         <v>3128200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2684800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2671900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2413600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2007200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1703500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2335800</v>
       </c>
-      <c r="K72" s="3"/>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="3"/>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -2316,9 +2495,12 @@
       <c r="J73" s="3">
         <v>0</v>
       </c>
-      <c r="K73" s="3"/>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K73" s="3">
+        <v>0</v>
+      </c>
+      <c r="L73" s="3"/>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -2343,9 +2525,12 @@
       <c r="J74" s="3">
         <v>0</v>
       </c>
-      <c r="K74" s="3"/>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K74" s="3">
+        <v>0</v>
+      </c>
+      <c r="L74" s="3"/>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -2370,36 +2555,42 @@
       <c r="J75" s="3">
         <v>0</v>
       </c>
-      <c r="K75" s="3"/>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K75" s="3">
+        <v>0</v>
+      </c>
+      <c r="L75" s="3"/>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>3152100</v>
+      </c>
+      <c r="E76" s="3">
         <v>3134600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2739200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2648000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2239300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2002500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1719600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2218800</v>
       </c>
-      <c r="K76" s="3"/>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L76" s="3"/>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -2424,68 +2615,77 @@
       <c r="J77" s="3">
         <v>0</v>
       </c>
-      <c r="K77" s="3"/>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K77" s="3">
+        <v>0</v>
+      </c>
+      <c r="L77" s="3"/>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2"/>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L80" s="2"/>
+    </row>
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>461200</v>
+      </c>
+      <c r="E81" s="3">
         <v>610700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>522900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>706600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>606100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>660300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>678700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>643000</v>
       </c>
-      <c r="K81" s="3"/>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3"/>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -2497,35 +2697,39 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>405500</v>
+      </c>
+      <c r="E83" s="3">
         <v>268000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>251100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>256500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>266200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>226000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>166700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>171400</v>
       </c>
-      <c r="K83" s="3"/>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3"/>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -2550,9 +2754,12 @@
       <c r="J84" s="3">
         <v>0</v>
       </c>
-      <c r="K84" s="3"/>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K84" s="3">
+        <v>0</v>
+      </c>
+      <c r="L84" s="3"/>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -2577,9 +2784,12 @@
       <c r="J85" s="3">
         <v>0</v>
       </c>
-      <c r="K85" s="3"/>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K85" s="3">
+        <v>0</v>
+      </c>
+      <c r="L85" s="3"/>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -2604,9 +2814,12 @@
       <c r="J86" s="3">
         <v>0</v>
       </c>
-      <c r="K86" s="3"/>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K86" s="3">
+        <v>0</v>
+      </c>
+      <c r="L86" s="3"/>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -2631,9 +2844,12 @@
       <c r="J87" s="3">
         <v>0</v>
       </c>
-      <c r="K87" s="3"/>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K87" s="3">
+        <v>0</v>
+      </c>
+      <c r="L87" s="3"/>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -2658,36 +2874,42 @@
       <c r="J88" s="3">
         <v>0</v>
       </c>
-      <c r="K88" s="3"/>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K88" s="3">
+        <v>0</v>
+      </c>
+      <c r="L88" s="3"/>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>1079100</v>
+      </c>
+      <c r="E89" s="3">
         <v>1010900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>578800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1109400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1267300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1106300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>830700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>816400</v>
       </c>
-      <c r="K89" s="3"/>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L89" s="3"/>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -2699,35 +2921,39 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E91" s="3">
         <v>-280900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-243100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-297800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-295200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-247200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-263400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-221800</v>
       </c>
-      <c r="K91" s="3"/>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3"/>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -2752,9 +2978,12 @@
       <c r="J92" s="3">
         <v>0</v>
       </c>
-      <c r="K92" s="3"/>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K92" s="3">
+        <v>0</v>
+      </c>
+      <c r="L92" s="3"/>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -2779,36 +3008,42 @@
       <c r="J93" s="3">
         <v>0</v>
       </c>
-      <c r="K93" s="3"/>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K93" s="3">
+        <v>0</v>
+      </c>
+      <c r="L93" s="3"/>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-776800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-453900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-539700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-607700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-705100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-397100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-348100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-336000</v>
       </c>
-      <c r="K94" s="3"/>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3"/>
+    </row>
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -2820,35 +3055,39 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>258400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>318700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>278700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>354900</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>316600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>973400</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>462400</v>
       </c>
-      <c r="K96" s="3"/>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3"/>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -2873,9 +3112,12 @@
       <c r="J97" s="3">
         <v>0</v>
       </c>
-      <c r="K97" s="3"/>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K97" s="3">
+        <v>0</v>
+      </c>
+      <c r="L97" s="3"/>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -2900,9 +3142,12 @@
       <c r="J98" s="3">
         <v>0</v>
       </c>
-      <c r="K98" s="3"/>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K98" s="3">
+        <v>0</v>
+      </c>
+      <c r="L98" s="3"/>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -2927,88 +3172,100 @@
       <c r="J99" s="3">
         <v>0</v>
       </c>
-      <c r="K99" s="3"/>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K99" s="3">
+        <v>0</v>
+      </c>
+      <c r="L99" s="3"/>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>651300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-439600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-171900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1620500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-12700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-566900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-327700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-552400</v>
       </c>
-      <c r="K100" s="3"/>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3"/>
+    </row>
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>26200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-38200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>9100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>79100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-75800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>9600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>3800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-86600</v>
       </c>
-      <c r="K101" s="3"/>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3"/>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>979800</v>
+      </c>
+      <c r="E102" s="3">
         <v>79200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-123700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1039700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>473700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>151900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>158700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-158700</v>
       </c>
-      <c r="K102" s="3"/>
+      <c r="L102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/KNRRY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/KNRRY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="91">
   <si>
     <t>KNRRY</t>
   </si>
@@ -295,9 +295,6 @@
   </si>
   <si>
     <t xml:space="preserve">Change In Cash and Cash Equivalents </t>
-  </si>
-  <si>
-    <t>NA</t>
   </si>
 </sst>
 </file>
@@ -711,10 +708,10 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>8278700</v>
+        <v>8278300</v>
       </c>
       <c r="E8" s="3">
-        <v>8885700</v>
+        <v>8885800</v>
       </c>
       <c r="F8" s="3">
         <v>7753300</v>
@@ -741,7 +738,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>3892000</v>
+        <v>4025300</v>
       </c>
       <c r="E9" s="3">
         <v>4590500</v>
@@ -771,7 +768,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>4386700</v>
+        <v>4253000</v>
       </c>
       <c r="E10" s="3">
         <v>4295300</v>
@@ -814,11 +811,11 @@
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>91</v>
+      <c r="D12" s="3">
+        <v>75600</v>
       </c>
       <c r="E12" s="3">
-        <v>482800</v>
+        <v>68500</v>
       </c>
       <c r="F12" s="3">
         <v>385900</v>
@@ -874,11 +871,11 @@
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>91</v>
+      <c r="D14" s="3">
+        <v>75600</v>
       </c>
       <c r="E14" s="3">
-        <v>33600</v>
+        <v>25400</v>
       </c>
       <c r="F14" s="3">
         <v>19400</v>
@@ -905,10 +902,10 @@
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>405500</v>
+        <v>371700</v>
       </c>
       <c r="E15" s="3">
-        <v>367400</v>
+        <v>367000</v>
       </c>
       <c r="F15" s="3">
         <v>325600</v>
@@ -946,10 +943,10 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>7335900</v>
+        <v>7440700</v>
       </c>
       <c r="E17" s="3">
-        <v>7906100</v>
+        <v>7975000</v>
       </c>
       <c r="F17" s="3">
         <v>6972600</v>
@@ -976,10 +973,10 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>942900</v>
+        <v>837600</v>
       </c>
       <c r="E18" s="3">
-        <v>979700</v>
+        <v>910800</v>
       </c>
       <c r="F18" s="3">
         <v>780700</v>
@@ -1020,10 +1017,10 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>225900</v>
+        <v>45600</v>
       </c>
       <c r="E20" s="3">
-        <v>15500</v>
+        <v>-45300</v>
       </c>
       <c r="F20" s="3">
         <v>23600</v>
@@ -1050,10 +1047,10 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>1122500</v>
+        <v>1163700</v>
       </c>
       <c r="E21" s="3">
-        <v>1331600</v>
+        <v>1323100</v>
       </c>
       <c r="F21" s="3">
         <v>1082700</v>
@@ -1080,10 +1077,10 @@
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>111400</v>
+        <v>110800</v>
       </c>
       <c r="E22" s="3">
-        <v>111700</v>
+        <v>111600</v>
       </c>
       <c r="F22" s="3">
         <v>54000</v>
@@ -1110,10 +1107,10 @@
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>668200</v>
+        <v>667800</v>
       </c>
       <c r="E23" s="3">
-        <v>854200</v>
+        <v>854400</v>
       </c>
       <c r="F23" s="3">
         <v>736100</v>
@@ -1140,10 +1137,10 @@
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>174000</v>
+        <v>173900</v>
       </c>
       <c r="E24" s="3">
-        <v>217300</v>
+        <v>217800</v>
       </c>
       <c r="F24" s="3">
         <v>195100</v>
@@ -1200,10 +1197,10 @@
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>494200</v>
+        <v>493800</v>
       </c>
       <c r="E26" s="3">
-        <v>636900</v>
+        <v>636700</v>
       </c>
       <c r="F26" s="3">
         <v>541000</v>
@@ -1230,10 +1227,10 @@
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>461200</v>
+        <v>460700</v>
       </c>
       <c r="E27" s="3">
-        <v>610700</v>
+        <v>611300</v>
       </c>
       <c r="F27" s="3">
         <v>522900</v>
@@ -1380,10 +1377,10 @@
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>-225900</v>
+        <v>-45600</v>
       </c>
       <c r="E32" s="3">
-        <v>-15500</v>
+        <v>45300</v>
       </c>
       <c r="F32" s="3">
         <v>-23600</v>
@@ -1410,10 +1407,10 @@
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>461200</v>
+        <v>460700</v>
       </c>
       <c r="E33" s="3">
-        <v>610700</v>
+        <v>611300</v>
       </c>
       <c r="F33" s="3">
         <v>522900</v>
@@ -1470,10 +1467,10 @@
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>461200</v>
+        <v>460700</v>
       </c>
       <c r="E35" s="3">
-        <v>610700</v>
+        <v>611300</v>
       </c>
       <c r="F35" s="3">
         <v>522900</v>
@@ -1566,7 +1563,7 @@
         <v>2342900</v>
       </c>
       <c r="E41" s="3">
-        <v>1427400</v>
+        <v>1427000</v>
       </c>
       <c r="F41" s="3">
         <v>1434800</v>
@@ -1623,10 +1620,10 @@
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>1683500</v>
+        <v>1683400</v>
       </c>
       <c r="E43" s="3">
-        <v>1817600</v>
+        <v>1679000</v>
       </c>
       <c r="F43" s="3">
         <v>1699500</v>
@@ -1656,7 +1653,7 @@
         <v>1258900</v>
       </c>
       <c r="E44" s="3">
-        <v>1262700</v>
+        <v>1262300</v>
       </c>
       <c r="F44" s="3">
         <v>1220400</v>
@@ -1683,10 +1680,10 @@
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>322900</v>
+        <v>322000</v>
       </c>
       <c r="E45" s="3">
-        <v>487200</v>
+        <v>626700</v>
       </c>
       <c r="F45" s="3">
         <v>350000</v>
@@ -1713,10 +1710,10 @@
         <v>38</v>
       </c>
       <c r="D46" s="3">
-        <v>5608200</v>
+        <v>5607200</v>
       </c>
       <c r="E46" s="3">
-        <v>4994800</v>
+        <v>4995000</v>
       </c>
       <c r="F46" s="3">
         <v>4704800</v>
@@ -1743,10 +1740,10 @@
         <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>37600</v>
+        <v>37300</v>
       </c>
       <c r="E47" s="3">
-        <v>67200</v>
+        <v>67400</v>
       </c>
       <c r="F47" s="3">
         <v>85000</v>
@@ -1773,10 +1770,10 @@
         <v>40</v>
       </c>
       <c r="D48" s="3">
-        <v>1964100</v>
+        <v>1723800</v>
       </c>
       <c r="E48" s="3">
-        <v>1798200</v>
+        <v>1797300</v>
       </c>
       <c r="F48" s="3">
         <v>1689700</v>
@@ -1803,10 +1800,10 @@
         <v>41</v>
       </c>
       <c r="D49" s="3">
-        <v>1880900</v>
+        <v>1880100</v>
       </c>
       <c r="E49" s="3">
-        <v>1620900</v>
+        <v>1620400</v>
       </c>
       <c r="F49" s="3">
         <v>1560300</v>
@@ -1893,10 +1890,10 @@
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>225700</v>
+        <v>459700</v>
       </c>
       <c r="E52" s="3">
-        <v>467000</v>
+        <v>557100</v>
       </c>
       <c r="F52" s="3">
         <v>425800</v>
@@ -1953,10 +1950,10 @@
         <v>46</v>
       </c>
       <c r="D54" s="3">
-        <v>9970600</v>
+        <v>9953400</v>
       </c>
       <c r="E54" s="3">
-        <v>9117500</v>
+        <v>9117900</v>
       </c>
       <c r="F54" s="3">
         <v>8701000</v>
@@ -2011,10 +2008,10 @@
         <v>49</v>
       </c>
       <c r="D57" s="3">
-        <v>1168200</v>
+        <v>1167800</v>
       </c>
       <c r="E57" s="3">
-        <v>1328100</v>
+        <v>1328600</v>
       </c>
       <c r="F57" s="3">
         <v>1297400</v>
@@ -2041,10 +2038,10 @@
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>74600</v>
+        <v>998000</v>
       </c>
       <c r="E58" s="3">
-        <v>177800</v>
+        <v>213300</v>
       </c>
       <c r="F58" s="3">
         <v>285400</v>
@@ -2071,10 +2068,10 @@
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>2217900</v>
+        <v>1244400</v>
       </c>
       <c r="E59" s="3">
-        <v>1228200</v>
+        <v>1250100</v>
       </c>
       <c r="F59" s="3">
         <v>1191100</v>
@@ -2101,10 +2098,10 @@
         <v>52</v>
       </c>
       <c r="D60" s="3">
-        <v>3480400</v>
+        <v>3430000</v>
       </c>
       <c r="E60" s="3">
-        <v>2852000</v>
+        <v>2809800</v>
       </c>
       <c r="F60" s="3">
         <v>2866900</v>
@@ -2131,10 +2128,10 @@
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>499700</v>
+        <v>2288000</v>
       </c>
       <c r="E61" s="3">
-        <v>2098100</v>
+        <v>2062600</v>
       </c>
       <c r="F61" s="3">
         <v>2034800</v>
@@ -2161,10 +2158,10 @@
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>2370500</v>
+        <v>624300</v>
       </c>
       <c r="E62" s="3">
-        <v>521100</v>
+        <v>600200</v>
       </c>
       <c r="F62" s="3">
         <v>530000</v>
@@ -2281,10 +2278,10 @@
         <v>57</v>
       </c>
       <c r="D66" s="3">
-        <v>6733600</v>
+        <v>6716000</v>
       </c>
       <c r="E66" s="3">
-        <v>5908100</v>
+        <v>5908000</v>
       </c>
       <c r="F66" s="3">
         <v>5892500</v>
@@ -2445,10 +2442,10 @@
         <v>63</v>
       </c>
       <c r="D72" s="3">
-        <v>3120900</v>
+        <v>3120400</v>
       </c>
       <c r="E72" s="3">
-        <v>3128200</v>
+        <v>3128100</v>
       </c>
       <c r="F72" s="3">
         <v>2684800</v>
@@ -2565,10 +2562,10 @@
         <v>67</v>
       </c>
       <c r="D76" s="3">
-        <v>3152100</v>
+        <v>3152500</v>
       </c>
       <c r="E76" s="3">
-        <v>3134600</v>
+        <v>3134700</v>
       </c>
       <c r="F76" s="3">
         <v>2739200</v>
@@ -2660,10 +2657,10 @@
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>461200</v>
+        <v>460700</v>
       </c>
       <c r="E81" s="3">
-        <v>610700</v>
+        <v>611300</v>
       </c>
       <c r="F81" s="3">
         <v>522900</v>
@@ -2704,10 +2701,10 @@
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>405500</v>
+        <v>269200</v>
       </c>
       <c r="E83" s="3">
-        <v>268000</v>
+        <v>267500</v>
       </c>
       <c r="F83" s="3">
         <v>251100</v>
@@ -2884,10 +2881,10 @@
         <v>77</v>
       </c>
       <c r="D89" s="3">
-        <v>1079100</v>
+        <v>1078800</v>
       </c>
       <c r="E89" s="3">
-        <v>1010900</v>
+        <v>1011400</v>
       </c>
       <c r="F89" s="3">
         <v>578800</v>
@@ -2927,11 +2924,11 @@
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>91</v>
+      <c r="D91" s="3">
+        <v>-236000</v>
       </c>
       <c r="E91" s="3">
-        <v>-280900</v>
+        <v>-280800</v>
       </c>
       <c r="F91" s="3">
         <v>-243100</v>
@@ -3018,10 +3015,10 @@
         <v>82</v>
       </c>
       <c r="D94" s="3">
-        <v>-776800</v>
+        <v>-776500</v>
       </c>
       <c r="E94" s="3">
-        <v>-453900</v>
+        <v>-454300</v>
       </c>
       <c r="F94" s="3">
         <v>-539700</v>
@@ -3062,10 +3059,10 @@
         <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>273300</v>
       </c>
       <c r="E96" s="3">
-        <v>258400</v>
+        <v>258600</v>
       </c>
       <c r="F96" s="3">
         <v>318700</v>
@@ -3182,10 +3179,10 @@
         <v>88</v>
       </c>
       <c r="D100" s="3">
-        <v>651300</v>
+        <v>652200</v>
       </c>
       <c r="E100" s="3">
-        <v>-439600</v>
+        <v>-439900</v>
       </c>
       <c r="F100" s="3">
         <v>-171900</v>
@@ -3212,10 +3209,10 @@
         <v>89</v>
       </c>
       <c r="D101" s="3">
-        <v>26200</v>
+        <v>25900</v>
       </c>
       <c r="E101" s="3">
-        <v>-38200</v>
+        <v>-38700</v>
       </c>
       <c r="F101" s="3">
         <v>9100</v>
@@ -3242,10 +3239,10 @@
         <v>90</v>
       </c>
       <c r="D102" s="3">
-        <v>979800</v>
+        <v>980400</v>
       </c>
       <c r="E102" s="3">
-        <v>79200</v>
+        <v>78500</v>
       </c>
       <c r="F102" s="3">
         <v>-123700</v>

--- a/AAII_Financials/Yearly/KNRRY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/KNRRY_YR_FIN.xlsx
@@ -812,10 +812,10 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>75600</v>
+        <v>476200</v>
       </c>
       <c r="E12" s="3">
-        <v>68500</v>
+        <v>483000</v>
       </c>
       <c r="F12" s="3">
         <v>385900</v>

--- a/AAII_Financials/Yearly/KNRRY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/KNRRY_YR_FIN.xlsx
@@ -653,147 +653,159 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>9282600</v>
+      </c>
+      <c r="E8" s="3">
         <v>8278300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>8885800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7753300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7720600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>7624300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>7866500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>7629800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>7427100</v>
       </c>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4384200</v>
+      </c>
+      <c r="E9" s="3">
         <v>4025300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>4590500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>4109800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3899000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3749900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3960700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3873000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3693100</v>
       </c>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4898400</v>
+      </c>
+      <c r="E10" s="3">
         <v>4253000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4295300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3643500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3821600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3874400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3905800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3756800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3734100</v>
       </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -806,38 +818,42 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>499000</v>
+      </c>
+      <c r="E12" s="3">
         <v>476200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>483000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>385900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>396100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>391800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>363100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>361300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>392700</v>
       </c>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -865,69 +881,78 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E14" s="3">
         <v>75600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>25400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>19400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-6700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>24400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>72200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>18700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-7300</v>
       </c>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>443800</v>
+      </c>
+      <c r="E15" s="3">
         <v>371700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>367000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>325600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>320700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>328500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>278900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>213500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>253900</v>
       </c>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -937,68 +962,75 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>7440700</v>
+        <v>8208300</v>
       </c>
       <c r="E17" s="3">
+        <v>7396200</v>
+      </c>
+      <c r="F17" s="3">
         <v>7975000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6972600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6702400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6598900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6692900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6497600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6348900</v>
       </c>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>837600</v>
+        <v>1074300</v>
       </c>
       <c r="E18" s="3">
+        <v>882100</v>
+      </c>
+      <c r="F18" s="3">
         <v>910800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>780700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1018200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1025300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1173600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1132100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1078300</v>
       </c>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1011,158 +1043,174 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>45600</v>
+        <v>11700</v>
       </c>
       <c r="E20" s="3">
+        <v>90100</v>
+      </c>
+      <c r="F20" s="3">
         <v>-45300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>23600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-23000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>24800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>32800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>71800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>44200</v>
       </c>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>1506400</v>
+      </c>
+      <c r="E21" s="3">
         <v>1163700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1323100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1082700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1361900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1329100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1419600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1273800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1288000</v>
       </c>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>147900</v>
+      </c>
+      <c r="E22" s="3">
         <v>110800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>111600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>54000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>64200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>81700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>81600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>62300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>46600</v>
       </c>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>961600</v>
+      </c>
+      <c r="E23" s="3">
         <v>667800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>854400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>736100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1001700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>918100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1018000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1002400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1023600</v>
       </c>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>290000</v>
+      </c>
+      <c r="E24" s="3">
         <v>173900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>217800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>195100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>265500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>267100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>308700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>281700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>318500</v>
       </c>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1190,69 +1238,78 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>671600</v>
+      </c>
+      <c r="E26" s="3">
         <v>493800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>636700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>541000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>736200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>651000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>709300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>720700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>705100</v>
       </c>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>627000</v>
+      </c>
+      <c r="E27" s="3">
         <v>460700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>611300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>522900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>706600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>606100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>660300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>678700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>643000</v>
       </c>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1280,9 +1337,12 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-      <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1310,9 +1370,12 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3"/>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1340,9 +1403,12 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-      <c r="L30" s="3"/>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1370,69 +1436,78 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-      <c r="L31" s="3"/>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>-45600</v>
+        <v>-11700</v>
       </c>
       <c r="E32" s="3">
+        <v>-90100</v>
+      </c>
+      <c r="F32" s="3">
         <v>45300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-23600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>23000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-24800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-32800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-71800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-44200</v>
       </c>
-      <c r="L32" s="3"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>627000</v>
+      </c>
+      <c r="E33" s="3">
         <v>460700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>611300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>522900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>706600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>606100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>660300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>678700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>643000</v>
       </c>
-      <c r="L33" s="3"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1460,74 +1535,83 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-      <c r="L34" s="3"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>627000</v>
+      </c>
+      <c r="E35" s="3">
         <v>460700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>611300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>522900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>706600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>606100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>660300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>678700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>643000</v>
       </c>
-      <c r="L35" s="3"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1540,8 +1624,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1554,38 +1639,42 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>2040600</v>
+      </c>
+      <c r="E41" s="3">
         <v>2342900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1427000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1434800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1569700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2785400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2110600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2010600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1921300</v>
       </c>
-      <c r="L41" s="3"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -1613,219 +1702,243 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-      <c r="L42" s="3"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>1727100</v>
+      </c>
+      <c r="E43" s="3">
         <v>1683400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1679000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1699500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1634400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1625700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1554500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1709800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1669800</v>
       </c>
-      <c r="L43" s="3"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>1241000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1258900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1262300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1220400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1139700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1033100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>914600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>957600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>899200</v>
       </c>
-      <c r="L44" s="3"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>740900</v>
+      </c>
+      <c r="E45" s="3">
         <v>322000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>626700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>350000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>134400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>179400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>159600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>57700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>141500</v>
       </c>
-      <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>5749700</v>
+      </c>
+      <c r="E46" s="3">
         <v>5607200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4995000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4704800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4478200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5623600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4739300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4774900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4631700</v>
       </c>
-      <c r="L46" s="3"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>54000</v>
+      </c>
+      <c r="E47" s="3">
         <v>37300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>67400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>85000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>25100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>30200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>18600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2300</v>
       </c>
-      <c r="L47" s="3"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>1879800</v>
+      </c>
+      <c r="E48" s="3">
         <v>1723800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1797300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1689700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1754600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1615500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1435100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1137500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1203900</v>
       </c>
-      <c r="L48" s="3"/>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>2019500</v>
+      </c>
+      <c r="E49" s="3">
         <v>1880100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1620400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1560300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1089900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1039500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>848200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>640000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>642800</v>
       </c>
-      <c r="L49" s="3"/>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -1853,9 +1966,12 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-      <c r="L50" s="3"/>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -1883,39 +1999,45 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-      <c r="L51" s="3"/>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>494300</v>
+      </c>
+      <c r="E52" s="3">
         <v>459700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>557100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>425800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>634700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>537300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>458600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>425800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>294500</v>
       </c>
-      <c r="L52" s="3"/>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -1943,39 +2065,45 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-      <c r="L53" s="3"/>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>10429700</v>
+      </c>
+      <c r="E54" s="3">
         <v>9953400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>9117900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8701000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8187400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>9039700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7683500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7169900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6877300</v>
       </c>
-      <c r="L54" s="3"/>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -1988,8 +2116,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -2002,188 +2131,207 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>1282100</v>
+      </c>
+      <c r="E57" s="3">
         <v>1167800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1328600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1297400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1326100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1257100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1085700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1140300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1073600</v>
       </c>
-      <c r="L57" s="3"/>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>236000</v>
+      </c>
+      <c r="E58" s="3">
         <v>998000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>213300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>285400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>180500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1386400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>255800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>81100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>47700</v>
       </c>
-      <c r="L58" s="3"/>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>1540400</v>
+      </c>
+      <c r="E59" s="3">
         <v>1244400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1250100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1191100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1552000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1524300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1343500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1406500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1553600</v>
       </c>
-      <c r="L59" s="3"/>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>3078500</v>
+      </c>
+      <c r="E60" s="3">
         <v>3430000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2809800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2866900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3067600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4271600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2819800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2713500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2766300</v>
       </c>
-      <c r="L60" s="3"/>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>2539600</v>
+      </c>
+      <c r="E61" s="3">
         <v>2288000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2062600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2034800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1398800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1356500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1790000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1648500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>869600</v>
       </c>
-      <c r="L61" s="3"/>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>622300</v>
+      </c>
+      <c r="E62" s="3">
         <v>624300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>600200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>530000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>427200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>461600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>437100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>489100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>388200</v>
       </c>
-      <c r="L62" s="3"/>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2211,9 +2359,12 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-      <c r="L63" s="3"/>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2241,9 +2392,12 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-      <c r="L64" s="3"/>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -2271,39 +2425,45 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-      <c r="L65" s="3"/>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>6696000</v>
+      </c>
+      <c r="E66" s="3">
         <v>6716000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5908000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5892500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5428900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6689100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5549600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5329900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4480900</v>
       </c>
-      <c r="L66" s="3"/>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -2316,8 +2476,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -2345,9 +2506,12 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-      <c r="L68" s="3"/>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -2375,9 +2539,12 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-      <c r="L69" s="3"/>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -2405,9 +2572,12 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="L70" s="3"/>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -2435,39 +2605,45 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-      <c r="L71" s="3"/>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
-        <v>3120400</v>
+        <v>3806500</v>
       </c>
       <c r="E72" s="3">
+        <v>3121400</v>
+      </c>
+      <c r="F72" s="3">
         <v>3128100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2684800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2671900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2413600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2007200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1703500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2335800</v>
       </c>
-      <c r="L72" s="3"/>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -2495,9 +2671,12 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-      <c r="L73" s="3"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -2525,9 +2704,12 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-      <c r="L74" s="3"/>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -2555,39 +2737,45 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-      <c r="L75" s="3"/>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>3644500</v>
+      </c>
+      <c r="E76" s="3">
         <v>3152500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3134700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2739200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2648000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2239300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2002500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1719600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2218800</v>
       </c>
-      <c r="L76" s="3"/>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -2615,74 +2803,83 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-      <c r="L77" s="3"/>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2"/>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>627000</v>
+      </c>
+      <c r="E81" s="3">
         <v>460700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>611300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>522900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>706600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>606100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>660300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>678700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>643000</v>
       </c>
-      <c r="L81" s="3"/>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -2695,38 +2892,42 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>308800</v>
+      </c>
+      <c r="E83" s="3">
         <v>269200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>267500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>251100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>256500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>266200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>226000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>166700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>171400</v>
       </c>
-      <c r="L83" s="3"/>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -2754,9 +2955,12 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-      <c r="L84" s="3"/>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -2784,9 +2988,12 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-      <c r="L85" s="3"/>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -2814,9 +3021,12 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-      <c r="L86" s="3"/>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -2844,9 +3054,12 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-      <c r="L87" s="3"/>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -2874,39 +3087,45 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-      <c r="L88" s="3"/>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>1310300</v>
+      </c>
+      <c r="E89" s="3">
         <v>1078800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1011400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>578800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1109400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1267300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1106300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>830700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>816400</v>
       </c>
-      <c r="L89" s="3"/>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -2919,38 +3138,42 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-277100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-236000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-280800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-243100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-297800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-295200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-247200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-263400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-221800</v>
       </c>
-      <c r="L91" s="3"/>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -2978,9 +3201,12 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-      <c r="L92" s="3"/>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -3008,39 +3234,45 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-      <c r="L93" s="3"/>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-359300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-776500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-454300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-539700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-607700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-705100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-397100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-348100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-336000</v>
       </c>
-      <c r="L94" s="3"/>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -3053,38 +3285,42 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>331100</v>
+      </c>
+      <c r="E96" s="3">
         <v>273300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>258600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>318700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>278700</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>354900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>316600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>973400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>462400</v>
       </c>
-      <c r="L96" s="3"/>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -3112,9 +3348,12 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-      <c r="L97" s="3"/>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -3142,9 +3381,12 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-      <c r="L98" s="3"/>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -3172,97 +3414,109 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-      <c r="L99" s="3"/>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-1474700</v>
+      </c>
+      <c r="E100" s="3">
         <v>652200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-439900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-171900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1620500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-12700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-566900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-327700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-552400</v>
       </c>
-      <c r="L100" s="3"/>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>-84500</v>
+      </c>
+      <c r="E101" s="3">
         <v>25900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-38700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>9100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>79100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-75800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>9600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>3800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-86600</v>
       </c>
-      <c r="L101" s="3"/>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-608200</v>
+      </c>
+      <c r="E102" s="3">
         <v>980400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>78500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-123700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1039700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>473700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>151900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>158700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-158700</v>
       </c>
-      <c r="L102" s="3"/>
+      <c r="M102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
